--- a/02_Glider_Design/C_results/nausicaa_results_iter2.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_results_iter2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/hl3422_ic_ac_uk/Documents/Year 4/Final Year Project/01 - Github/Nausicaa/02_Glider_Design/C_results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_95C14C4074A96E424B128B68C3E85A3A9EE053CD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57176C87-091A-46AF-A953-34A805C847C1}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_95C14C4074A96E424B128B68C3E85A3A9EE053CD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF8D4BB7-36A3-538D-A035-51F62B598409}"/>
   <bookViews>
-    <workbookView xWindow="21840" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>

--- a/02_Glider_Design/C_results/nausicaa_results_iter2.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_results_iter2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/hl3422_ic_ac_uk/Documents/Year 4/Final Year Project/01 - Github/Nausicaa/02_Glider_Design/C_results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_95C14C4074A96E424B128B68C3E85A3A9EE053CD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF8D4BB7-36A3-538D-A035-51F62B598409}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_95C14C4074A96E424B128B68C3E85A3A9EE053CD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C6EE1DC-08C5-4F0A-BEBA-BEA668AEEC0B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21840" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -1342,6 +1342,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C76"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="29.54296875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -2189,6 +2192,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.08984375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
